--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/05_AddClaimTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/05_AddClaimTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\ClaimPoints\ClaimPoints\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B2B82B-BE7C-405F-8181-3EFF62738ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35657D01-BA2C-4C0E-9D6B-A42DF6C217C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="46">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -28,9 +28,6 @@
     <t>TEST_DESC</t>
   </si>
   <si>
-    <t>COMPANY_NAME</t>
-  </si>
-  <si>
     <t>EXPECTED_RESULT</t>
   </si>
   <si>
@@ -49,12 +46,6 @@
     <t>MODULE_NAME</t>
   </si>
   <si>
-    <t>2601000018</t>
-  </si>
-  <si>
-    <t>ClaimPoints</t>
-  </si>
-  <si>
     <t>AddClaimTest_01</t>
   </si>
   <si>
@@ -161,6 +152,12 @@
   </si>
   <si>
     <t>AddClaimTest_18</t>
+  </si>
+  <si>
+    <t>2602000005</t>
+  </si>
+  <si>
+    <t>02_ClaimPoints</t>
   </si>
 </sst>
 </file>
@@ -1090,7 +1087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.90625" style="2" bestFit="1" customWidth="1"/>
@@ -1098,18 +1095,17 @@
     <col min="3" max="3" width="24.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="71.26953125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="56.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.453125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="57.1796875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.90625" style="2"/>
+    <col min="6" max="6" width="57.1796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>7</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>8</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>0</v>
@@ -1118,318 +1114,303 @@
         <v>1</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="5" t="s">
+      <c r="G1" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>10</v>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-    </row>
-    <row r="14" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/05_AddClaimTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/05_AddClaimTest.xlsx
@@ -8,19 +8,37 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35657D01-BA2C-4C0E-9D6B-A42DF6C217C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A985E4BA-5042-49ED-986D-F7F0B0307145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TestCases!$A$1:$O$7</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="112">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -67,12 +85,6 @@
     <t>Verify Total claim Points on claim details</t>
   </si>
   <si>
-    <t>Verify  claim id on claim details</t>
-  </si>
-  <si>
-    <t>Verify  product code &amp; name  on claim details</t>
-  </si>
-  <si>
     <t>Verify  Claim Qty  on claim details</t>
   </si>
   <si>
@@ -158,6 +170,292 @@
   </si>
   <si>
     <t>02_ClaimPoints</t>
+  </si>
+  <si>
+    <t>INVOICE001</t>
+  </si>
+  <si>
+    <t>CATEGORY_NAME</t>
+  </si>
+  <si>
+    <t>BRAND_NAME</t>
+  </si>
+  <si>
+    <t>PRODUCT_NAME</t>
+  </si>
+  <si>
+    <t>QTY</t>
+  </si>
+  <si>
+    <t>Cement</t>
+  </si>
+  <si>
+    <t>Ambuja Cement</t>
+  </si>
+  <si>
+    <t>Ambj001</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>After Submit Claim verify Success Toast msg.</t>
+  </si>
+  <si>
+    <t>verifypagetitle</t>
+  </si>
+  <si>
+    <t>Claim Details</t>
+  </si>
+  <si>
+    <t>CUTOMER_NAME</t>
+  </si>
+  <si>
+    <t>CUSTOMER_MOBILE</t>
+  </si>
+  <si>
+    <t>SITE_ADDRESS</t>
+  </si>
+  <si>
+    <t>Dhruv Pande</t>
+  </si>
+  <si>
+    <t>5467835678</t>
+  </si>
+  <si>
+    <t>Kothrud</t>
+  </si>
+  <si>
+    <t>Verify  claim id on claim details, it should not be null or Empty.</t>
+  </si>
+  <si>
+    <t>Verify  product code  on claim details</t>
+  </si>
+  <si>
+    <t>Verify  product Description  on claim details</t>
+  </si>
+  <si>
+    <t>AddClaimTest_19</t>
+  </si>
+  <si>
+    <t>AddClaimTest_20</t>
+  </si>
+  <si>
+    <t>verify_claimdetails_dealername</t>
+  </si>
+  <si>
+    <t>verify_claimdetails_productcode</t>
+  </si>
+  <si>
+    <t>verify_claimdetails_claim_invno</t>
+  </si>
+  <si>
+    <t>verify_claimdetails_claim_invdate</t>
+  </si>
+  <si>
+    <t>verify_claimdetails_claim_totalpointsonheader</t>
+  </si>
+  <si>
+    <t>{SELECTED_DEALERNAME}</t>
+  </si>
+  <si>
+    <t>{INVOICE_DATE}</t>
+  </si>
+  <si>
+    <t>{INVOICE_NO}</t>
+  </si>
+  <si>
+    <t>{CARD_TOTAL_CLAIMPOINTS}</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>{CATEGORY_PRODUCTCODE}</t>
+  </si>
+  <si>
+    <t>{CATEGORY_PRODUCTDESC}</t>
+  </si>
+  <si>
+    <t>Verify  Claim Qty UOM  on claim details</t>
+  </si>
+  <si>
+    <t>{CATEGORY_PRODUCTUOM}</t>
+  </si>
+  <si>
+    <t>verify_claimdetails_claimid</t>
+  </si>
+  <si>
+    <t>verify_claimdetails_productdesc</t>
+  </si>
+  <si>
+    <t>AddClaimTest_21</t>
+  </si>
+  <si>
+    <t>{PRODUCT_QTY}</t>
+  </si>
+  <si>
+    <t>verify_claimdetails_uom</t>
+  </si>
+  <si>
+    <t>verify_claimdetails_claim_qty</t>
+  </si>
+  <si>
+    <t>verify_claimdetails_claim_points</t>
+  </si>
+  <si>
+    <t>{CARDDETAILS_POINTS}</t>
+  </si>
+  <si>
+    <t>{CARDDETAILS_TOTALPOINTS}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">openclaimpointsmenu
+myclaims_clickonfabbutton
+dealerlist_clickonradiobutton
+dealer_enterinvno
+dealer_clickonimagecaptureicon
+clickonbrowsefileoption
+selectimageclickonbrowsefileoption
+dealerpage_getdealername
+dealerpage_getinvdate
+dealerpage_getinvno
+dealer_clickonnextbutton
+category_selectcategory
+category_selectbrand
+category_enterproductname_insearchfield
+hidekeyboard
+category_enterqty
+hidekeyboard
+category_productcode_inlist
+category_productdesc_inlist
+category_clickon_addtocart_btn
+category_clickon_carticon
+cartdetails_get_totalclaimpoints
+cartdetails_clickon_updownarrow
+cartdetails_get_points
+cartdetails_get_totalpoints
+cartdetails_clickon_submitbtn
+claiminfo_enter_customername
+claiminfo_enter_customermobileno
+claiminfo_enter_siteaddress
+claiminfo_clikon_sitephotoicon
+clickonbrowsefileoption
+selectimageclickonbrowsefileoption
+claiminfo_clikon_materialproductimageicon
+clickonbrowsefileoption
+selectimageclickonbrowsefileoption
+claiminfo_clikon_submitbtn
+claiminfo_clikon_alertbox_yesbtn
+verify_warningmsg
+</t>
+  </si>
+  <si>
+    <t>verify_claimdetails_claim_totalpoints</t>
+  </si>
+  <si>
+    <t>claimdetails_clickon_pdficon
+verify_claimdetails_pdfdownloadstratedtext</t>
+  </si>
+  <si>
+    <t>claimdetails_getclaim_id
+claimdetails_clickon_closebtn
+verify_navigatetodashboard</t>
+  </si>
+  <si>
+    <t>{GENERATED_CLAIMID}</t>
+  </si>
+  <si>
+    <t>verify_claimid_onclaimdetails</t>
+  </si>
+  <si>
+    <t>AddClaimTest_22</t>
+  </si>
+  <si>
+    <t>Verify added claim claim product desc on My Claims page</t>
+  </si>
+  <si>
+    <t>verify_myclaims_generated_invno</t>
+  </si>
+  <si>
+    <t>verify_myclaims_generated_dealername</t>
+  </si>
+  <si>
+    <t>verify_myclaims_generated_productdesc</t>
+  </si>
+  <si>
+    <t>verify_myclaims_generated_claimqty</t>
+  </si>
+  <si>
+    <t>verify_myclaims_generated_claimpoints</t>
+  </si>
+  <si>
+    <t>CONTAINS</t>
+  </si>
+  <si>
+    <t>myclaims_get_addedclaimclaimdetails
+verify_myclaims_generated_invdate</t>
+  </si>
+  <si>
+    <t>{GENERATED_TOTALPOINTS}</t>
+  </si>
+  <si>
+    <t>INV_NO</t>
+  </si>
+  <si>
+    <t>Claim Submitted Successfully.</t>
+  </si>
+  <si>
+    <t>openclaimpointsmenu
+verify_claimid_onclaimdetails</t>
+  </si>
+  <si>
+    <t xml:space="preserve">openclaimpointsmenu
+myclaims_clickonfabbutton
+dealerlist_clickonradiobutton
+dealer_enterinvno
+dealer_clickonimagecaptureicon
+clickonbrowsefileoption
+selectimageclickonbrowsefileoption
+dealerpage_getdealernamebysplit
+dealerpage_getinvdate
+dealerpage_getinvno
+dealer_clickonnextbutton
+category_selectcategory
+category_selectbrand
+category_enterproductname_insearchfield
+hidekeyboard
+category_enterqty
+hidekeyboard
+category_productcode_inlist
+category_productdesc_inlist
+category_clickon_addtocart_btn
+category_clickon_carticon
+cartdetails_get_totalclaimpoints
+cartdetails_clickon_updownarrow
+cartdetails_get_points
+cartdetails_get_totalpoints
+cartdetails_clickon_submitbtn
+claiminfo_enter_customername
+claiminfo_enter_customermobileno
+claiminfo_enter_siteaddress
+claiminfo_clikon_sitephotoicon
+clickonbrowsefileoption
+selectimageclickonbrowsefileoption
+claiminfo_clikon_materialproductimageicon
+clickonbrowsefileoption
+selectimageclickonbrowsefileoption
+claiminfo_clikon_submitbtn
+claiminfo_clikon_alertbox_yesbtn
+verify_warningmsg
+</t>
+  </si>
+  <si>
+    <t>verify_myclaims_generated_invdate</t>
+  </si>
+  <si>
+    <t>verify_myclaims_generated_claimpoints
+navigatebacktodashboardpage</t>
   </si>
 </sst>
 </file>
@@ -312,7 +610,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -498,8 +796,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -653,6 +963,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -699,7 +1022,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -711,6 +1034,15 @@
     <xf numFmtId="49" fontId="13" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="13" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1087,20 +1419,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.90625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="71.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="56.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="57.1796875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.90625" style="2"/>
+    <col min="4" max="4" width="57.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.7265625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="17" style="2" customWidth="1"/>
+    <col min="13" max="13" width="13.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
@@ -1117,305 +1457,2046 @@
         <v>3</v>
       </c>
       <c r="F1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="1"/>
+        <v>62</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-    </row>
-    <row r="14" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>37</v>
+      <c r="E20" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O7" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}"/>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81092E69-F1E0-4FD3-BDE6-FBF13ADF732D}">
+  <dimension ref="A1:O23"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.7265625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="17" style="2" customWidth="1"/>
+    <col min="13" max="13" width="13.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.90625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="O17" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O18" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O19" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O20" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O21" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O22" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2070842-9E41-431F-999E-017B10B60F5F}">
+  <dimension ref="A1:O20"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.7265625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="17" style="2" customWidth="1"/>
+    <col min="13" max="13" width="13.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.90625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O15" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/05_AddClaimTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/05_AddClaimTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A985E4BA-5042-49ED-986D-F7F0B0307145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{902BF0E3-FD65-4237-8A4F-5DC0A19E6C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -610,7 +610,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -805,6 +805,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1022,7 +1028,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1043,6 +1049,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="18" fillId="36" borderId="10" xfId="42" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1506,13 +1516,13 @@
       <c r="F2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="15" t="s">
         <v>51</v>
       </c>
       <c r="J2" s="4" t="s">

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/05_AddClaimTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/05_AddClaimTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{902BF0E3-FD65-4237-8A4F-5DC0A19E6C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF89D891-0D59-4517-A411-8FCC5F94FA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="113">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -456,6 +456,11 @@
   <si>
     <t>verify_myclaims_generated_claimpoints
 navigatebacktodashboardpage</t>
+  </si>
+  <si>
+    <t>navigatebacktodashboardpage
+openclaimpointsmenu
+verify_claimid_onclaimdetails</t>
   </si>
 </sst>
 </file>
@@ -1900,7 +1905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>42</v>
       </c>
@@ -1914,7 +1919,7 @@
         <v>30</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/05_AddClaimTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/05_AddClaimTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF89D891-0D59-4517-A411-8FCC5F94FA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97749DA9-CF81-4453-A5AB-C353C78C24D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/05_AddClaimTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/05_AddClaimTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97749DA9-CF81-4453-A5AB-C353C78C24D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E149FEE-B39A-4FCB-B5FC-862CA46E5877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="115">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -461,6 +461,12 @@
     <t>navigatebacktodashboardpage
 openclaimpointsmenu
 verify_claimid_onclaimdetails</t>
+  </si>
+  <si>
+    <t>APPIUM Cement</t>
+  </si>
+  <si>
+    <t>APMCMT0001</t>
   </si>
 </sst>
 </file>
@@ -1525,10 +1531,10 @@
         <v>49</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>50</v>
+        <v>113</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>52</v>

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/05_AddClaimTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/05_AddClaimTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E149FEE-B39A-4FCB-B5FC-862CA46E5877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8F5E61-CBFF-4772-8DDB-AC5161B90C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -458,15 +458,17 @@
 navigatebacktodashboardpage</t>
   </si>
   <si>
+    <t>APPIUM Cement</t>
+  </si>
+  <si>
+    <t>APMCMT0001</t>
+  </si>
+  <si>
     <t>navigatebacktodashboardpage
 openclaimpointsmenu
+myclaims_enterfromdate_todaydate
+myclaims_entertodate_todaydate
 verify_claimid_onclaimdetails</t>
-  </si>
-  <si>
-    <t>APPIUM Cement</t>
-  </si>
-  <si>
-    <t>APMCMT0001</t>
   </si>
 </sst>
 </file>
@@ -1531,10 +1533,10 @@
         <v>49</v>
       </c>
       <c r="H2" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="I2" s="15" t="s">
         <v>113</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>114</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>52</v>
@@ -1911,7 +1913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>42</v>
       </c>
@@ -1925,7 +1927,7 @@
         <v>30</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/05_AddClaimTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/05_AddClaimTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8F5E61-CBFF-4772-8DDB-AC5161B90C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C1BE52-F252-40EC-AC9F-2B73A6EF9EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TestCases!$A$1:$O$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TestCases!$A$1:$P$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="125">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -469,6 +469,36 @@
 myclaims_enterfromdate_todaydate
 myclaims_entertodate_todaydate
 verify_claimid_onclaimdetails</t>
+  </si>
+  <si>
+    <t>EXPECTED_KEY</t>
+  </si>
+  <si>
+    <t>SELECTED_DEALERNAMESPLIT</t>
+  </si>
+  <si>
+    <t>INVOICE_NO</t>
+  </si>
+  <si>
+    <t>INVOICE_DATE</t>
+  </si>
+  <si>
+    <t>CARD_TOTAL_CLAIMPOINTS</t>
+  </si>
+  <si>
+    <t>CATEGORY_PRODUCTCODE</t>
+  </si>
+  <si>
+    <t>CATEGORY_PRODUCTDESC</t>
+  </si>
+  <si>
+    <t>PRODUCT_QTY</t>
+  </si>
+  <si>
+    <t>CARDDETAILS_TOTALPOINTS</t>
+  </si>
+  <si>
+    <t>SELECTED_DEALERNAME</t>
   </si>
 </sst>
 </file>
@@ -1041,7 +1071,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1066,6 +1096,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="18" fillId="35" borderId="10" xfId="42" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1442,7 +1477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}">
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.90625" style="2" bestFit="1" customWidth="1"/>
@@ -1458,12 +1493,13 @@
     <col min="11" max="11" width="16.7265625" style="2" customWidth="1"/>
     <col min="12" max="12" width="17" style="2" customWidth="1"/>
     <col min="13" max="13" width="13.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="25.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.90625" style="2"/>
+    <col min="14" max="14" width="25.90625" style="18" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
@@ -1504,13 +1540,16 @@
         <v>58</v>
       </c>
       <c r="N1" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="O1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>42</v>
       </c>
@@ -1550,14 +1589,15 @@
       <c r="M2" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="16"/>
+      <c r="O2" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>42</v>
       </c>
@@ -1581,14 +1621,15 @@
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="16"/>
+      <c r="O3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>42</v>
       </c>
@@ -1612,12 +1653,15 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1" t="s">
+      <c r="N4" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>42</v>
       </c>
@@ -1641,12 +1685,15 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N5" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>42</v>
       </c>
@@ -1670,12 +1717,15 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N6" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>42</v>
       </c>
@@ -1699,12 +1749,15 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N7" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>42</v>
       </c>
@@ -1728,14 +1781,15 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
-      <c r="N8" s="1" t="s">
+      <c r="N8" s="13"/>
+      <c r="O8" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="O8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>42</v>
       </c>
@@ -1759,12 +1813,15 @@
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N9" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>42</v>
       </c>
@@ -1788,12 +1845,15 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N10" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>42</v>
       </c>
@@ -1817,12 +1877,15 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N11" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>42</v>
       </c>
@@ -1846,12 +1909,15 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="N12" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>42</v>
       </c>
@@ -1875,14 +1941,15 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
-      <c r="N13" s="1" t="s">
+      <c r="N13" s="13"/>
+      <c r="O13" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="O13" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="P13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>42</v>
       </c>
@@ -1906,14 +1973,15 @@
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
-      <c r="N14" s="8" t="s">
+      <c r="N14" s="17"/>
+      <c r="O14" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="O14" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="P14" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>42</v>
       </c>
@@ -1937,14 +2005,15 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
-      <c r="N15" s="1" t="s">
+      <c r="N15" s="13"/>
+      <c r="O15" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="O15" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -1968,12 +2037,15 @@
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1" t="s">
+      <c r="N16" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>42</v>
       </c>
@@ -1997,12 +2069,15 @@
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N17" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>42</v>
       </c>
@@ -2026,12 +2101,15 @@
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N18" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
@@ -2055,12 +2133,15 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="N19" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>42</v>
       </c>
@@ -2084,13 +2165,16 @@
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1" t="s">
+      <c r="N20" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O7" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}"/>
+  <autoFilter ref="A1:P7" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}"/>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
